--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/41.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/41.xlsx
@@ -426,13 +426,13 @@
         <v>-5.745818014524103</v>
       </c>
       <c r="E2">
-        <v>-11.00737743257396</v>
+        <v>-9.81776542465499</v>
       </c>
       <c r="F2">
-        <v>-2.512116245018719</v>
+        <v>-1.645187511251494</v>
       </c>
       <c r="G2">
-        <v>-7.837390180222627</v>
+        <v>-6.891735564347541</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.888827733946996</v>
       </c>
       <c r="E3">
-        <v>-12.29000429661048</v>
+        <v>-10.62108048582365</v>
       </c>
       <c r="F3">
-        <v>-2.41191361050648</v>
+        <v>-1.558114500073627</v>
       </c>
       <c r="G3">
-        <v>-7.849848978483839</v>
+        <v>-6.38479995829957</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.155431160178155</v>
       </c>
       <c r="E4">
-        <v>-12.13279832143421</v>
+        <v>-10.35455714810221</v>
       </c>
       <c r="F4">
-        <v>-2.221975591983776</v>
+        <v>-1.036291909986703</v>
       </c>
       <c r="G4">
-        <v>-7.629347608467594</v>
+        <v>-6.263411166707913</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.501800986829808</v>
       </c>
       <c r="E5">
-        <v>-12.8255506897056</v>
+        <v>-11.22191388868735</v>
       </c>
       <c r="F5">
-        <v>-2.331904916539687</v>
+        <v>-1.096254112805748</v>
       </c>
       <c r="G5">
-        <v>-7.865582435861376</v>
+        <v>-5.916714015515424</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.888230841389655</v>
       </c>
       <c r="E6">
-        <v>-13.10527000068539</v>
+        <v>-11.42130712771908</v>
       </c>
       <c r="F6">
-        <v>-2.23852637269171</v>
+        <v>-1.258993516024933</v>
       </c>
       <c r="G6">
-        <v>-7.899214956845684</v>
+        <v>-5.987384965462745</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.254558079440591</v>
       </c>
       <c r="E7">
-        <v>-13.17883506093999</v>
+        <v>-11.51974256722381</v>
       </c>
       <c r="F7">
-        <v>-2.218352312963931</v>
+        <v>-0.8260539198909943</v>
       </c>
       <c r="G7">
-        <v>-7.474099891604027</v>
+        <v>-6.279574464109738</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.544428038462888</v>
       </c>
       <c r="E8">
-        <v>-13.59525088831532</v>
+        <v>-13.92991417443017</v>
       </c>
       <c r="F8">
-        <v>-2.03427416544863</v>
+        <v>-0.7428295036665337</v>
       </c>
       <c r="G8">
-        <v>-7.135589388202353</v>
+        <v>-5.543570218553812</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.704970105503913</v>
       </c>
       <c r="E9">
-        <v>-14.5423948124416</v>
+        <v>-12.19112053817899</v>
       </c>
       <c r="F9">
-        <v>-1.891167069675793</v>
+        <v>-0.7819673783466019</v>
       </c>
       <c r="G9">
-        <v>-7.177520118510497</v>
+        <v>-5.352803278309255</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.698842044760669</v>
       </c>
       <c r="E10">
-        <v>-14.99797741150927</v>
+        <v>-13.8207688938973</v>
       </c>
       <c r="F10">
-        <v>-1.840493350544339</v>
+        <v>-0.9221710463726266</v>
       </c>
       <c r="G10">
-        <v>-7.358896202651922</v>
+        <v>-5.871000036749241</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.509728957785249</v>
       </c>
       <c r="E11">
-        <v>-15.37835111425755</v>
+        <v>-15.16805330981534</v>
       </c>
       <c r="F11">
-        <v>-1.771387628333193</v>
+        <v>-0.4622805167886054</v>
       </c>
       <c r="G11">
-        <v>-6.886554515505177</v>
+        <v>-4.948651937610891</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.145280648707642</v>
       </c>
       <c r="E12">
-        <v>-15.90059285071812</v>
+        <v>-13.82851711292443</v>
       </c>
       <c r="F12">
-        <v>-1.503191256165811</v>
+        <v>-0.6906407005553592</v>
       </c>
       <c r="G12">
-        <v>-6.796875449063994</v>
+        <v>-5.171338601185726</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.632948247841991</v>
       </c>
       <c r="E13">
-        <v>-16.61079342934107</v>
+        <v>-15.0927538440158</v>
       </c>
       <c r="F13">
-        <v>-1.055515003936069</v>
+        <v>-0.8961569964551109</v>
       </c>
       <c r="G13">
-        <v>-6.138337563304999</v>
+        <v>-3.849140842813442</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.023132024518663</v>
       </c>
       <c r="E14">
-        <v>-18.19231769177986</v>
+        <v>-16.82674276934484</v>
       </c>
       <c r="F14">
-        <v>-1.384877196758763</v>
+        <v>-0.3619793065554329</v>
       </c>
       <c r="G14">
-        <v>-6.274915129495326</v>
+        <v>-4.311025276850237</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.373981986696863</v>
       </c>
       <c r="E15">
-        <v>-19.12499314145163</v>
+        <v>-17.1612339734474</v>
       </c>
       <c r="F15">
-        <v>-1.139542108173842</v>
+        <v>0.3759005546318659</v>
       </c>
       <c r="G15">
-        <v>-6.159212694866186</v>
+        <v>-3.851539415773396</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.744867707183277</v>
       </c>
       <c r="E16">
-        <v>-19.24446334272199</v>
+        <v>-18.04658686973902</v>
       </c>
       <c r="F16">
-        <v>-0.8979984571915343</v>
+        <v>0.2629799953844457</v>
       </c>
       <c r="G16">
-        <v>-5.35254406180606</v>
+        <v>-3.619071430729857</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.189468352326761</v>
       </c>
       <c r="E17">
-        <v>-20.68841709328177</v>
+        <v>-18.62390390708088</v>
       </c>
       <c r="F17">
-        <v>-0.4931719939738046</v>
+        <v>1.181689975500668</v>
       </c>
       <c r="G17">
-        <v>-5.470021637298859</v>
+        <v>-2.425297402972681</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.740196520592118</v>
       </c>
       <c r="E18">
-        <v>-20.31231826999673</v>
+        <v>-19.89346612360528</v>
       </c>
       <c r="F18">
-        <v>0.09612609127555528</v>
+        <v>1.208775932837406</v>
       </c>
       <c r="G18">
-        <v>-4.637395260481965</v>
+        <v>-2.730365696240494</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.408115174313171</v>
       </c>
       <c r="E19">
-        <v>-20.97573971212044</v>
+        <v>-20.05589342931239</v>
       </c>
       <c r="F19">
-        <v>0.1653850614562191</v>
+        <v>1.091106343269737</v>
       </c>
       <c r="G19">
-        <v>-5.056505690269838</v>
+        <v>-2.306280934568502</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.185482530048337</v>
       </c>
       <c r="E20">
-        <v>-21.71341454254792</v>
+        <v>-19.07326891133602</v>
       </c>
       <c r="F20">
-        <v>0.5724588854377438</v>
+        <v>1.574147256659796</v>
       </c>
       <c r="G20">
-        <v>-4.455815740603854</v>
+        <v>-1.721107881657131</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.044531278430374</v>
       </c>
       <c r="E21">
-        <v>-21.74943855327893</v>
+        <v>-21.80600825058275</v>
       </c>
       <c r="F21">
-        <v>0.8039030810451201</v>
+        <v>1.365476537690183</v>
       </c>
       <c r="G21">
-        <v>-3.997015654832937</v>
+        <v>-2.241437434110755</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.954195246065995</v>
       </c>
       <c r="E22">
-        <v>-22.62993692543433</v>
+        <v>-22.16491245806067</v>
       </c>
       <c r="F22">
-        <v>0.6751433086887705</v>
+        <v>1.951016320033042</v>
       </c>
       <c r="G22">
-        <v>-3.997045185826972</v>
+        <v>-2.737669695431817</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.883028596623874</v>
       </c>
       <c r="E23">
-        <v>-23.06731505899116</v>
+        <v>-22.77792292753099</v>
       </c>
       <c r="F23">
-        <v>0.8272381907819821</v>
+        <v>1.824461661702945</v>
       </c>
       <c r="G23">
-        <v>-4.603300087257775</v>
+        <v>-2.853772439091209</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.802416804646689</v>
       </c>
       <c r="E24">
-        <v>-23.94709340377933</v>
+        <v>-22.424883093893</v>
       </c>
       <c r="F24">
-        <v>1.042774418785997</v>
+        <v>2.467077614833495</v>
       </c>
       <c r="G24">
-        <v>-3.972222744729773</v>
+        <v>-2.165696996854093</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.697118803372918</v>
       </c>
       <c r="E25">
-        <v>-23.90970632237201</v>
+        <v>-23.63916622820577</v>
       </c>
       <c r="F25">
-        <v>1.292055021310452</v>
+        <v>1.990763044754168</v>
       </c>
       <c r="G25">
-        <v>-4.339128939506881</v>
+        <v>-0.8927109994303615</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.558469226030738</v>
       </c>
       <c r="E26">
-        <v>-23.14712488490234</v>
+        <v>-23.70220258639254</v>
       </c>
       <c r="F26">
-        <v>1.104204488642802</v>
+        <v>2.236985314827487</v>
       </c>
       <c r="G26">
-        <v>-3.668814749571039</v>
+        <v>-2.746131965833625</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.389372062878532</v>
       </c>
       <c r="E27">
-        <v>-24.52780226815294</v>
+        <v>-23.38037299561542</v>
       </c>
       <c r="F27">
-        <v>1.03127667923514</v>
+        <v>2.131636862009057</v>
       </c>
       <c r="G27">
-        <v>-4.121334577277178</v>
+        <v>-2.10130302374999</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.2028391576544</v>
       </c>
       <c r="E28">
-        <v>-23.90151431289213</v>
+        <v>-23.66822997438699</v>
       </c>
       <c r="F28">
-        <v>0.8794700689981022</v>
+        <v>1.948395365570584</v>
       </c>
       <c r="G28">
-        <v>-4.18077390582652</v>
+        <v>-2.55766516190224</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.01261052816967</v>
       </c>
       <c r="E29">
-        <v>-22.32477211900544</v>
+        <v>-21.60629801837048</v>
       </c>
       <c r="F29">
-        <v>0.818401167328917</v>
+        <v>1.907480642811511</v>
       </c>
       <c r="G29">
-        <v>-4.018002347927146</v>
+        <v>-2.766239291549903</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.834598335330322</v>
       </c>
       <c r="E30">
-        <v>-23.0936119075537</v>
+        <v>-22.96104988792717</v>
       </c>
       <c r="F30">
-        <v>1.027244186718312</v>
+        <v>2.29246107979297</v>
       </c>
       <c r="G30">
-        <v>-3.644871675851771</v>
+        <v>-1.208065922287034</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.682715804889363</v>
       </c>
       <c r="E31">
-        <v>-22.27293920551364</v>
+        <v>-22.63117772731243</v>
       </c>
       <c r="F31">
-        <v>0.7896336241644958</v>
+        <v>1.684286986536018</v>
       </c>
       <c r="G31">
-        <v>-3.429515261240736</v>
+        <v>-1.665878360368558</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.565457674964313</v>
       </c>
       <c r="E32">
-        <v>-22.38193051793025</v>
+        <v>-22.32502118507586</v>
       </c>
       <c r="F32">
-        <v>0.6946231965330036</v>
+        <v>1.367726383556187</v>
       </c>
       <c r="G32">
-        <v>-3.453231930672402</v>
+        <v>-4.148542466448094</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.488537138658754</v>
       </c>
       <c r="E33">
-        <v>-21.98107905571929</v>
+        <v>-20.99539781778773</v>
       </c>
       <c r="F33">
-        <v>0.2536873698598409</v>
+        <v>1.519900788920067</v>
       </c>
       <c r="G33">
-        <v>-3.000853195493319</v>
+        <v>-0.7113152279595792</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.451890641596189</v>
       </c>
       <c r="E34">
-        <v>-21.86720604832241</v>
+        <v>-20.93003835243503</v>
       </c>
       <c r="F34">
-        <v>0.114054446974345</v>
+        <v>2.005617329021169</v>
       </c>
       <c r="G34">
-        <v>-3.49898200287574</v>
+        <v>-2.469351083629785</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.449992181643601</v>
       </c>
       <c r="E35">
-        <v>-21.14019124570899</v>
+        <v>-21.61753316238351</v>
       </c>
       <c r="F35">
-        <v>0.2883777399542785</v>
+        <v>1.888925212988802</v>
       </c>
       <c r="G35">
-        <v>-3.892190469673357</v>
+        <v>-2.980352123189908</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.473769679650851</v>
       </c>
       <c r="E36">
-        <v>-20.71508074823893</v>
+        <v>-18.4694693579973</v>
       </c>
       <c r="F36">
-        <v>0.7487619765103681</v>
+        <v>1.973294432963932</v>
       </c>
       <c r="G36">
-        <v>-3.575132592827333</v>
+        <v>-1.449908357325906</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.510212666678564</v>
       </c>
       <c r="E37">
-        <v>-20.55389877288392</v>
+        <v>-20.50633168190735</v>
       </c>
       <c r="F37">
-        <v>0.3612376232349119</v>
+        <v>2.081815532935084</v>
       </c>
       <c r="G37">
-        <v>-3.773200251041653</v>
+        <v>-2.67661272465367</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.546338189814084</v>
       </c>
       <c r="E38">
-        <v>-20.90613253814854</v>
+        <v>-20.16846676466907</v>
       </c>
       <c r="F38">
-        <v>0.312657188530332</v>
+        <v>1.388397463725646</v>
       </c>
       <c r="G38">
-        <v>-3.63081492269111</v>
+        <v>-1.222467203711437</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.572233557263851</v>
       </c>
       <c r="E39">
-        <v>-19.90425294869155</v>
+        <v>-20.01631456648536</v>
       </c>
       <c r="F39">
-        <v>0.4340519463083912</v>
+        <v>2.165301713258829</v>
       </c>
       <c r="G39">
-        <v>-3.455279412925496</v>
+        <v>-1.847024759000822</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.580698428967482</v>
       </c>
       <c r="E40">
-        <v>-18.89419946365071</v>
+        <v>-20.20299637897756</v>
       </c>
       <c r="F40">
-        <v>0.4610492683330299</v>
+        <v>1.683127272172098</v>
       </c>
       <c r="G40">
-        <v>-3.462307789505826</v>
+        <v>-1.665317271481893</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.568154979616525</v>
       </c>
       <c r="E41">
-        <v>-18.68926337243359</v>
+        <v>-17.14857236012196</v>
       </c>
       <c r="F41">
-        <v>0.3779863837521151</v>
+        <v>1.876385387245223</v>
       </c>
       <c r="G41">
-        <v>-3.152865627899273</v>
+        <v>-1.454695659581136</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.533779887323974</v>
       </c>
       <c r="E42">
-        <v>-18.35846740312128</v>
+        <v>-17.77825667088852</v>
       </c>
       <c r="F42">
-        <v>0.05813964728537835</v>
+        <v>1.050256233168082</v>
       </c>
       <c r="G42">
-        <v>-4.110854355616312</v>
+        <v>-1.815082067119628</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.479027036369427</v>
       </c>
       <c r="E43">
-        <v>-18.13465210376619</v>
+        <v>-17.03656055554223</v>
       </c>
       <c r="F43">
-        <v>0.6524327879736193</v>
+        <v>1.358228322915688</v>
       </c>
       <c r="G43">
-        <v>-4.082041949102828</v>
+        <v>-2.463375979170036</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.408258960952128</v>
       </c>
       <c r="E44">
-        <v>-18.6358998347272</v>
+        <v>-17.62803360263207</v>
       </c>
       <c r="F44">
-        <v>0.07107626101489822</v>
+        <v>1.164004331450899</v>
       </c>
       <c r="G44">
-        <v>-3.743761131210316</v>
+        <v>-1.757362098667436</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.326156553711636</v>
       </c>
       <c r="E45">
-        <v>-16.69005983837133</v>
+        <v>-16.81472419932848</v>
       </c>
       <c r="F45">
-        <v>0.4247858285406759</v>
+        <v>1.258552530071629</v>
       </c>
       <c r="G45">
-        <v>-3.978306129500983</v>
+        <v>-1.46985818440733</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.238682337240235</v>
       </c>
       <c r="E46">
-        <v>-16.95745264310224</v>
+        <v>-15.39141576176967</v>
       </c>
       <c r="F46">
-        <v>0.5302543946325118</v>
+        <v>1.228013937400022</v>
       </c>
       <c r="G46">
-        <v>-4.528458704708401</v>
+        <v>-0.947520524359326</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.152540566970701</v>
       </c>
       <c r="E47">
-        <v>-16.321464696517</v>
+        <v>-17.09015504542301</v>
       </c>
       <c r="F47">
-        <v>0.2625807222962963</v>
+        <v>1.290782648979752</v>
       </c>
       <c r="G47">
-        <v>-3.705633336689568</v>
+        <v>-1.537717127478206</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.071706632834046</v>
       </c>
       <c r="E48">
-        <v>-16.171508808227</v>
+        <v>-14.74541535915347</v>
       </c>
       <c r="F48">
-        <v>0.1855905991453047</v>
+        <v>1.654803733935578</v>
       </c>
       <c r="G48">
-        <v>-4.031005828967225</v>
+        <v>-1.727562044464559</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.9987682980323382</v>
       </c>
       <c r="E49">
-        <v>-15.50679675101111</v>
+        <v>-15.2114225053868</v>
       </c>
       <c r="F49">
-        <v>0.04168247209396057</v>
+        <v>0.9641706359343516</v>
       </c>
       <c r="G49">
-        <v>-3.913951531055594</v>
+        <v>-1.714207472717619</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.9354830139392992</v>
       </c>
       <c r="E50">
-        <v>-14.92423574076836</v>
+        <v>-14.32916708531643</v>
       </c>
       <c r="F50">
-        <v>0.01440764698938405</v>
+        <v>0.7003869769216826</v>
       </c>
       <c r="G50">
-        <v>-4.285307062267309</v>
+        <v>-2.478298974822391</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.8816036449101409</v>
       </c>
       <c r="E51">
-        <v>-14.32717002827905</v>
+        <v>-13.52912158238131</v>
       </c>
       <c r="F51">
-        <v>0.05159637317066505</v>
+        <v>0.8367942371406772</v>
       </c>
       <c r="G51">
-        <v>-4.161158763344159</v>
+        <v>-2.142032826967378</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.8359720451247706</v>
       </c>
       <c r="E52">
-        <v>-13.91144252895289</v>
+        <v>-12.65322413981771</v>
       </c>
       <c r="F52">
-        <v>0.1161816944647341</v>
+        <v>0.6027837593194281</v>
       </c>
       <c r="G52">
-        <v>-4.605032572241162</v>
+        <v>-1.806163706921057</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.796046835896457</v>
       </c>
       <c r="E53">
-        <v>-12.66195050923049</v>
+        <v>-13.38660597688592</v>
       </c>
       <c r="F53">
-        <v>-0.1014039144938064</v>
+        <v>1.358254830672577</v>
       </c>
       <c r="G53">
-        <v>-4.920623743050114</v>
+        <v>-1.56062333518469</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.7596942361183143</v>
       </c>
       <c r="E54">
-        <v>-12.83039162841979</v>
+        <v>-12.50882921760913</v>
       </c>
       <c r="F54">
-        <v>-0.128182547524106</v>
+        <v>0.349953602473977</v>
       </c>
       <c r="G54">
-        <v>-3.910995150430534</v>
+        <v>-1.791014306981101</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.7268802746174869</v>
       </c>
       <c r="E55">
-        <v>-12.28140472446992</v>
+        <v>-12.60390905787418</v>
       </c>
       <c r="F55">
-        <v>0.260446019499282</v>
+        <v>0.9511553273015658</v>
       </c>
       <c r="G55">
-        <v>-4.576453132458398</v>
+        <v>-2.094550269780653</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.6977519964697928</v>
       </c>
       <c r="E56">
-        <v>-12.23568525088848</v>
+        <v>-11.8354768319866</v>
       </c>
       <c r="F56">
-        <v>-0.08741527416273118</v>
+        <v>0.9737183986190188</v>
       </c>
       <c r="G56">
-        <v>-5.065072959761548</v>
+        <v>-4.062088840799845</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.6729703287104356</v>
       </c>
       <c r="E57">
-        <v>-11.68618662937573</v>
+        <v>-11.64105585741529</v>
       </c>
       <c r="F57">
-        <v>-0.2376703522543251</v>
+        <v>1.194378907376751</v>
       </c>
       <c r="G57">
-        <v>-5.123685420477909</v>
+        <v>-1.387217338211156</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.6541737045442104</v>
       </c>
       <c r="E58">
-        <v>-12.4784069292256</v>
+        <v>-9.876979750779288</v>
       </c>
       <c r="F58">
-        <v>-0.06704903319750254</v>
+        <v>0.4654619814877429</v>
       </c>
       <c r="G58">
-        <v>-5.887783485025801</v>
+        <v>-3.005801277604961</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.6420309325460601</v>
       </c>
       <c r="E59">
-        <v>-11.64899427235074</v>
+        <v>-10.84744531604507</v>
       </c>
       <c r="F59">
-        <v>-0.04956385405921057</v>
+        <v>0.7685417333544148</v>
       </c>
       <c r="G59">
-        <v>-5.103246691384128</v>
+        <v>-2.836237591077537</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.6355877992858376</v>
       </c>
       <c r="E60">
-        <v>-11.25907454639429</v>
+        <v>-9.949077585455408</v>
       </c>
       <c r="F60">
-        <v>-0.5173727476465921</v>
+        <v>0.6128227438739553</v>
       </c>
       <c r="G60">
-        <v>-5.095224104671286</v>
+        <v>-2.193754722408904</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.6329487867335672</v>
       </c>
       <c r="E61">
-        <v>-11.06167836439994</v>
+        <v>-9.880462147291187</v>
       </c>
       <c r="F61">
-        <v>-0.2857156616166964</v>
+        <v>0.1771106020428461</v>
       </c>
       <c r="G61">
-        <v>-5.414660867147908</v>
+        <v>-2.62224616463523</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.6322058818288863</v>
       </c>
       <c r="E62">
-        <v>-10.28064792382302</v>
+        <v>-9.780310416137549</v>
       </c>
       <c r="F62">
-        <v>-0.5279617681565782</v>
+        <v>1.374419592170807</v>
       </c>
       <c r="G62">
-        <v>-5.218243663377987</v>
+        <v>-3.160638841773598</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.63285719256418</v>
       </c>
       <c r="E63">
-        <v>-9.649849608450573</v>
+        <v>-9.909448909414285</v>
       </c>
       <c r="F63">
-        <v>-0.3107364990182555</v>
+        <v>0.3769931712361584</v>
       </c>
       <c r="G63">
-        <v>-5.597539750763559</v>
+        <v>-2.947218347882635</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.6338562106637711</v>
       </c>
       <c r="E64">
-        <v>-10.44121402671299</v>
+        <v>-10.7719511258632</v>
       </c>
       <c r="F64">
-        <v>-0.8419453201463001</v>
+        <v>0.1606708225668872</v>
       </c>
       <c r="G64">
-        <v>-5.958628339715771</v>
+        <v>-3.191403575114951</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.6312655643177203</v>
       </c>
       <c r="E65">
-        <v>-9.81454115116153</v>
+        <v>-9.966924301519636</v>
       </c>
       <c r="F65">
-        <v>-0.6764110053100693</v>
+        <v>-0.2080404786235896</v>
       </c>
       <c r="G65">
-        <v>-5.328778174051002</v>
+        <v>-4.099235550074318</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.6195675199259207</v>
       </c>
       <c r="E66">
-        <v>-9.902728653986902</v>
+        <v>-8.814088031016956</v>
       </c>
       <c r="F66">
-        <v>-0.9224303253697028</v>
+        <v>-0.05516444606953803</v>
       </c>
       <c r="G66">
-        <v>-6.02293043861621</v>
+        <v>-3.780038316771536</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.5927990785962445</v>
       </c>
       <c r="E67">
-        <v>-9.304490066729601</v>
+        <v>-8.201620978427554</v>
       </c>
       <c r="F67">
-        <v>-0.9700639361328828</v>
+        <v>0.06573329126684142</v>
       </c>
       <c r="G67">
-        <v>-4.933003791993899</v>
+        <v>-2.851436209340885</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.5460069805802202</v>
       </c>
       <c r="E68">
-        <v>-9.974269486360079</v>
+        <v>-9.808137888914683</v>
       </c>
       <c r="F68">
-        <v>-0.9567553854395059</v>
+        <v>0.1373092050731355</v>
       </c>
       <c r="G68">
-        <v>-5.91833493896579</v>
+        <v>-3.981393758988421</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.4772435227725295</v>
       </c>
       <c r="E69">
-        <v>-10.19660397471467</v>
+        <v>-8.997201405991115</v>
       </c>
       <c r="F69">
-        <v>-0.8596201954198331</v>
+        <v>-0.1662178651910481</v>
       </c>
       <c r="G69">
-        <v>-6.178194561587574</v>
+        <v>-3.55553057523121</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.3865771781687485</v>
       </c>
       <c r="E70">
-        <v>-10.30540961969696</v>
+        <v>-8.945599444673711</v>
       </c>
       <c r="F70">
-        <v>-1.108207454428145</v>
+        <v>-0.5019634572197158</v>
       </c>
       <c r="G70">
-        <v>-5.027207662965557</v>
+        <v>-3.424708271656149</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.2765706897033989</v>
       </c>
       <c r="E71">
-        <v>-9.82826242740477</v>
+        <v>-9.138362997758215</v>
       </c>
       <c r="F71">
-        <v>-1.330282814709859</v>
+        <v>-0.1463105397669704</v>
       </c>
       <c r="G71">
-        <v>-5.222266441009866</v>
+        <v>-4.28736766940664</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.1516857096743572</v>
       </c>
       <c r="E72">
-        <v>-10.54196804490965</v>
+        <v>-9.242105808799934</v>
       </c>
       <c r="F72">
-        <v>-1.064398415963691</v>
+        <v>-0.8176832672857054</v>
       </c>
       <c r="G72">
-        <v>-4.922441539794046</v>
+        <v>-4.530676810482585</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.01610879289205265</v>
       </c>
       <c r="E73">
-        <v>-10.24398539825692</v>
+        <v>-9.492892699344718</v>
       </c>
       <c r="F73">
-        <v>-1.681177589800924</v>
+        <v>-0.4657339804908766</v>
       </c>
       <c r="G73">
-        <v>-4.919061881587818</v>
+        <v>-3.520395254772676</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.1246341894998328</v>
       </c>
       <c r="E74">
-        <v>-11.36951949896736</v>
+        <v>-9.842970910981684</v>
       </c>
       <c r="F74">
-        <v>-1.836995983369719</v>
+        <v>-0.6804766325230093</v>
       </c>
       <c r="G74">
-        <v>-4.520570648079495</v>
+        <v>-2.80365834221381</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.2640516312220632</v>
       </c>
       <c r="E75">
-        <v>-11.1895941696946</v>
+        <v>-9.735532865149704</v>
       </c>
       <c r="F75">
-        <v>-1.809639149892266</v>
+        <v>-0.4521330161043115</v>
       </c>
       <c r="G75">
-        <v>-4.508128255926081</v>
+        <v>-2.368151648293391</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.3941602823999774</v>
       </c>
       <c r="E76">
-        <v>-11.71127437537823</v>
+        <v>-10.28585114045784</v>
       </c>
       <c r="F76">
-        <v>-1.577513207912385</v>
+        <v>-0.7168063417075872</v>
       </c>
       <c r="G76">
-        <v>-4.169519315877624</v>
+        <v>-2.762574167068003</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.5067689348333462</v>
       </c>
       <c r="E77">
-        <v>-11.11565324609736</v>
+        <v>-11.2592556853546</v>
       </c>
       <c r="F77">
-        <v>-1.919628116901178</v>
+        <v>-1.191136971857209</v>
       </c>
       <c r="G77">
-        <v>-4.667884371212326</v>
+        <v>-2.480172552332834</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.5947154516627636</v>
       </c>
       <c r="E78">
-        <v>-11.81888903169651</v>
+        <v>-10.6157368864946</v>
       </c>
       <c r="F78">
-        <v>-1.640368898069409</v>
+        <v>-0.9945363943137886</v>
       </c>
       <c r="G78">
-        <v>-4.004227779820597</v>
+        <v>-3.000475855013983</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.6498642323338349</v>
       </c>
       <c r="E79">
-        <v>-12.6826229930755</v>
+        <v>-13.36247373889904</v>
       </c>
       <c r="F79">
-        <v>-1.729600634698972</v>
+        <v>-0.8234188831826891</v>
       </c>
       <c r="G79">
-        <v>-3.845531499098053</v>
+        <v>-4.121239421851954</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.6649038455036135</v>
       </c>
       <c r="E80">
-        <v>-12.12015482200479</v>
+        <v>-11.11875977926662</v>
       </c>
       <c r="F80">
-        <v>-2.071870448392088</v>
+        <v>-1.073179938800768</v>
       </c>
       <c r="G80">
-        <v>-3.719129000963564</v>
+        <v>-2.477495075540327</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.63216806198855</v>
       </c>
       <c r="E81">
-        <v>-12.95103923293215</v>
+        <v>-11.46760171749949</v>
       </c>
       <c r="F81">
-        <v>-1.71422530733561</v>
+        <v>-1.454679575955664</v>
       </c>
       <c r="G81">
-        <v>-2.937049842269916</v>
+        <v>-2.311908229542949</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.5449557724872273</v>
       </c>
       <c r="E82">
-        <v>-15.01157189048029</v>
+        <v>-13.52812531809962</v>
       </c>
       <c r="F82">
-        <v>-2.04098808324832</v>
+        <v>-1.507835912193308</v>
       </c>
       <c r="G82">
-        <v>-3.554264023709264</v>
+        <v>-2.751221140472324</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.4005475417516794</v>
       </c>
       <c r="E83">
-        <v>-14.28126035878929</v>
+        <v>-13.63234814738616</v>
       </c>
       <c r="F83">
-        <v>-2.209024896008408</v>
+        <v>-1.563148488780439</v>
       </c>
       <c r="G83">
-        <v>-2.688851681070399</v>
+        <v>-2.946319293175347</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.1956509041363286</v>
       </c>
       <c r="E84">
-        <v>-16.23495725754847</v>
+        <v>-15.59185507829718</v>
       </c>
       <c r="F84">
-        <v>-2.498455638179153</v>
+        <v>-0.9491078975768609</v>
       </c>
       <c r="G84">
-        <v>-3.872955948891892</v>
+        <v>-1.642988558769871</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.06813324686343804</v>
       </c>
       <c r="E85">
-        <v>-16.53214289277584</v>
+        <v>-16.51040621753903</v>
       </c>
       <c r="F85">
-        <v>-2.290303477203693</v>
+        <v>-1.403757346603369</v>
       </c>
       <c r="G85">
-        <v>-2.743159179100768</v>
+        <v>-2.220079962980329</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.3849475037801401</v>
       </c>
       <c r="E86">
-        <v>-17.91805519197931</v>
+        <v>-16.9618588483117</v>
       </c>
       <c r="F86">
-        <v>-2.721850587733526</v>
+        <v>-1.786294928113973</v>
       </c>
       <c r="G86">
-        <v>-2.573808771974708</v>
+        <v>-1.359983199267764</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.7502007015843037</v>
       </c>
       <c r="E87">
-        <v>-18.83446436301553</v>
+        <v>-18.6202539570307</v>
       </c>
       <c r="F87">
-        <v>-2.568395526364918</v>
+        <v>-1.478909322487549</v>
       </c>
       <c r="G87">
-        <v>-2.718661578937954</v>
+        <v>-3.023345969283312</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.154409069680205</v>
       </c>
       <c r="E88">
-        <v>-20.66884955709462</v>
+        <v>-19.66011385799002</v>
       </c>
       <c r="F88">
-        <v>-2.711471972543851</v>
+        <v>-1.558173314159225</v>
       </c>
       <c r="G88">
-        <v>-2.579567315811533</v>
+        <v>-1.882852417208399</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.58881404195866</v>
       </c>
       <c r="E89">
-        <v>-21.86427612563945</v>
+        <v>-22.93445416008012</v>
       </c>
       <c r="F89">
-        <v>-2.984080229498543</v>
+        <v>-1.915007483528363</v>
       </c>
       <c r="G89">
-        <v>-2.538525796545999</v>
+        <v>-2.197255785812832</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.044156595856387</v>
       </c>
       <c r="E90">
-        <v>-23.30687586247093</v>
+        <v>-25.0979733735107</v>
       </c>
       <c r="F90">
-        <v>-2.99648337462066</v>
+        <v>-1.228923779303311</v>
       </c>
       <c r="G90">
-        <v>-2.812219049262401</v>
+        <v>-2.120032236411301</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.507108012767884</v>
       </c>
       <c r="E91">
-        <v>-24.88440148236095</v>
+        <v>-23.83169882911588</v>
       </c>
       <c r="F91">
-        <v>-2.936172429125036</v>
+        <v>-2.341116362058817</v>
       </c>
       <c r="G91">
-        <v>-2.118588498925145</v>
+        <v>-0.5031873444440009</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.97047100267249</v>
       </c>
       <c r="E92">
-        <v>-26.88801575010669</v>
+        <v>-27.1482082811654</v>
       </c>
       <c r="F92">
-        <v>-3.421752288604676</v>
+        <v>-1.985241442142122</v>
       </c>
       <c r="G92">
-        <v>-2.731071158875774</v>
+        <v>-1.752945574448423</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.425590838666612</v>
       </c>
       <c r="E93">
-        <v>-28.55982419883641</v>
+        <v>-28.27751912919824</v>
       </c>
       <c r="F93">
-        <v>-3.363641486930888</v>
+        <v>-2.484275644978031</v>
       </c>
       <c r="G93">
-        <v>-2.542328732333395</v>
+        <v>-2.484552983114693</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.862232744198915</v>
       </c>
       <c r="E94">
-        <v>-30.40112437272521</v>
+        <v>-30.84741001465513</v>
       </c>
       <c r="F94">
-        <v>-3.546833281325193</v>
+        <v>-2.555639496729208</v>
       </c>
       <c r="G94">
-        <v>-2.851829955928018</v>
+        <v>-1.259111886087315</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.277194350321945</v>
       </c>
       <c r="E95">
-        <v>-33.05317762634028</v>
+        <v>-33.65400876496697</v>
       </c>
       <c r="F95">
-        <v>-3.079996891068698</v>
+        <v>-2.354864775843081</v>
       </c>
       <c r="G95">
-        <v>-2.739028121157427</v>
+        <v>-2.539267352618433</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.66111528285484</v>
       </c>
       <c r="E96">
-        <v>-34.67800089300341</v>
+        <v>-34.65806655042164</v>
       </c>
       <c r="F96">
-        <v>-3.39523210620405</v>
+        <v>-2.445223920507853</v>
       </c>
       <c r="G96">
-        <v>-2.493648529277473</v>
+        <v>-2.417304347253873</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.006717369375421</v>
       </c>
       <c r="E97">
-        <v>-37.49531174858039</v>
+        <v>-38.1985248918095</v>
       </c>
       <c r="F97">
-        <v>-3.509510359624659</v>
+        <v>-2.978914530374686</v>
       </c>
       <c r="G97">
-        <v>-3.219983014897715</v>
+        <v>-1.838427958515077</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.309630081061519</v>
       </c>
       <c r="E98">
-        <v>-39.99570867191558</v>
+        <v>-38.85939227459288</v>
       </c>
       <c r="F98">
-        <v>-3.836037879194973</v>
+        <v>-3.245387069976842</v>
       </c>
       <c r="G98">
-        <v>-3.539977585039442</v>
+        <v>-1.133408288144988</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.564579351364078</v>
       </c>
       <c r="E99">
-        <v>-42.03352876807825</v>
+        <v>-43.95533162440141</v>
       </c>
       <c r="F99">
-        <v>-3.99879550649702</v>
+        <v>-3.19082582262405</v>
       </c>
       <c r="G99">
-        <v>-3.578807560973911</v>
+        <v>-2.419994948932618</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.76564955150911</v>
       </c>
       <c r="E100">
-        <v>-45.14910077145942</v>
+        <v>-45.02367109839497</v>
       </c>
       <c r="F100">
-        <v>-4.149813510966593</v>
+        <v>-2.703664609772466</v>
       </c>
       <c r="G100">
-        <v>-3.452155690000904</v>
+        <v>-2.518293784410463</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.907687276585738</v>
       </c>
       <c r="E101">
-        <v>-47.1660808302388</v>
+        <v>-46.73825777683815</v>
       </c>
       <c r="F101">
-        <v>-4.335916188414335</v>
+        <v>-3.684962717374608</v>
       </c>
       <c r="G101">
-        <v>-3.526600044741586</v>
+        <v>-2.962443215918459</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.973763164955574</v>
       </c>
       <c r="E102">
-        <v>-50.60605459763345</v>
+        <v>-49.53094279076142</v>
       </c>
       <c r="F102">
-        <v>-4.372062828402894</v>
+        <v>-3.430081522839825</v>
       </c>
       <c r="G102">
-        <v>-4.368830557062974</v>
+        <v>-2.276969782377982</v>
       </c>
     </row>
   </sheetData>
